--- a/cards_gnb_updated.xlsx
+++ b/cards_gnb_updated.xlsx
@@ -204,6 +204,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F4E78"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>▶</t>
     </r>
     <r>
@@ -336,6 +343,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>绝枪基础的晶壤攻击，放进初始牌组中作为使用晶壤的</t>
     </r>
     <r>
@@ -689,6 +701,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>原</t>
     </r>
     <r>
@@ -1331,6 +1348,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>对应观者猛虎下山（</t>
     </r>
     <r>
@@ -1411,6 +1433,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>对照</t>
     </r>
     <r>
@@ -1743,6 +1770,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>抽</t>
     </r>
     <r>
@@ -1764,6 +1796,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>对照</t>
     </r>
     <r>
@@ -1848,6 +1885,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>和</t>
     </r>
     <r>
@@ -4904,7 +4946,7 @@
         <v>43</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>34</v>
+        <v>141</v>
       </c>
       <c r="F37" s="3">
         <v>1</v>

--- a/cards_gnb_updated.xlsx
+++ b/cards_gnb_updated.xlsx
@@ -694,18 +694,70 @@
     <t>终结技</t>
   </si>
   <si>
-    <t>获得2档晶壤，在抽牌堆中放入一张【崛起之心】</t>
-  </si>
-  <si>
-    <t>获得2档晶壤，在抽牌堆中放入一张【崛起之心+】</t>
-  </si>
-  <si>
+    <r>
+      <t>获得</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
+      <t>档晶壤，在抽牌堆顶部放入一张【崛起之心】</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>获得</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>档晶壤，在抽牌堆顶部放入一张【崛起之心</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>】</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>原</t>
     </r>
     <r>
@@ -882,10 +934,94 @@
     <t>主目标+其他敌人</t>
   </si>
   <si>
-    <t>对指定敌人造成25点伤害，对其他敌人造成5点伤害，在抽牌堆中放入一张【支配之心】</t>
-  </si>
-  <si>
-    <t>对指定敌人造成30点伤害，对其他敌人造成6点伤害，在抽牌堆中放入一张【支配之心+】</t>
+    <r>
+      <t>对指定敌人造成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点伤害，对其他敌人造成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点伤害，在抽牌堆顶部放入一张【支配之心】</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>对指定敌人造成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点伤害，对其他敌人造成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点伤害，在抽牌堆顶部放入一张【支配之心</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>】</t>
+    </r>
   </si>
   <si>
     <t>DamageMain</t>
@@ -906,10 +1042,94 @@
     <t>Noble Blood</t>
   </si>
   <si>
-    <t>对指定敌人造成35点伤害，对其他敌人造成7点伤害，在抽牌堆中放入一张【终结之心】</t>
-  </si>
-  <si>
-    <t>对指定敌人造成40点伤害，对其他敌人造成8点伤害，在抽牌堆中放入一张【终结之心+】</t>
+    <r>
+      <t>对指定敌人造成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>35</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点伤害，对其他敌人造成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点伤害，在抽牌堆顶部放入一张【终结之心】</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>对指定敌人造成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点伤害，对其他敌人造成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点伤害，在抽牌堆顶部放入一张【终结之心</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>】</t>
+    </r>
   </si>
   <si>
     <t>LionHeart</t>
@@ -4304,10 +4524,10 @@
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
-      <c r="P25" s="3" t="s">
+      <c r="P25" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="Q25" s="3" t="s">
+      <c r="Q25" s="5" t="s">
         <v>150</v>
       </c>
       <c r="R25" s="3" t="s">
@@ -4367,10 +4587,10 @@
       </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
-      <c r="P26" s="3" t="s">
+      <c r="P26" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="Q26" s="3" t="s">
+      <c r="Q26" s="5" t="s">
         <v>157</v>
       </c>
       <c r="R26" s="3" t="s">
@@ -4436,10 +4656,10 @@
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
-      <c r="P27" s="3" t="s">
+      <c r="P27" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="Q27" s="3" t="s">
+      <c r="Q27" s="5" t="s">
         <v>165</v>
       </c>
       <c r="R27" s="3" t="s">
